--- a/AAII_Financials/Yearly/FBRT_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/FBRT_YR_FIN.xlsx
@@ -2573,10 +2573,10 @@
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>3753000</v>
+        <v>1017500</v>
       </c>
       <c r="E58" s="3">
-        <v>3965700</v>
+        <v>337400</v>
       </c>
       <c r="F58" s="3">
         <v>3818100</v>
@@ -2657,10 +2657,10 @@
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>3882700</v>
+        <v>1147100</v>
       </c>
       <c r="E60" s="3">
-        <v>4032900</v>
+        <v>404700</v>
       </c>
       <c r="F60" s="3">
         <v>3914600</v>
@@ -2699,10 +2699,10 @@
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>514700</v>
+        <v>3250300</v>
       </c>
       <c r="E61" s="3">
-        <v>348000</v>
+        <v>3976300</v>
       </c>
       <c r="F61" s="3">
         <v>364700</v>
